--- a/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+  <si>
+    <t>1,//玩家
+2,//怪物</t>
+  </si>
   <si>
     <t>#</t>
   </si>
@@ -80,58 +84,22 @@
     <t>玩家Unit</t>
   </si>
   <si>
-    <t>字母哥</t>
-  </si>
-  <si>
-    <t>宝鱼猎杀者</t>
+    <t>战斗爽</t>
+  </si>
+  <si>
+    <t>史莱姆猎杀者</t>
   </si>
   <si>
     <t>Knight</t>
   </si>
   <si>
-    <t>关卡怪物</t>
-  </si>
-  <si>
-    <t>弱鸡宝鱼</t>
-  </si>
-  <si>
-    <t>吃饭睡觉打宝鱼</t>
-  </si>
-  <si>
-    <t>BaoYu</t>
-  </si>
-  <si>
-    <t>新兵宝鱼</t>
-  </si>
-  <si>
-    <t>精英宝鱼</t>
-  </si>
-  <si>
-    <t>专家宝鱼</t>
-  </si>
-  <si>
-    <t>大师宝鱼</t>
-  </si>
-  <si>
-    <t>英雄宝鱼</t>
-  </si>
-  <si>
-    <t>传奇宝鱼</t>
-  </si>
-  <si>
-    <t>半神宝鱼</t>
-  </si>
-  <si>
-    <t>圣灵宝鱼</t>
-  </si>
-  <si>
-    <t>神灵宝鱼</t>
-  </si>
-  <si>
-    <t>永生宝鱼</t>
-  </si>
-  <si>
-    <t>创世宝鱼</t>
+    <t>森林:简单怪是史莱姆组</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+  </si>
+  <si>
+    <t>Slime</t>
   </si>
 </sst>
 </file>
@@ -144,7 +112,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,12 +128,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -632,168 +594,164 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1142,13 +1100,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:J18"/>
+  <dimension ref="C1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="26.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
     <col min="8" max="8" width="7.875" style="2" customWidth="1"/>
@@ -1157,422 +1115,229 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:5">
+    <row r="1" ht="84" customHeight="1" spans="3:10">
+      <c r="D1" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="3:10">
       <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="3:10">
+      <c r="C3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="3:10">
+      <c r="C4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="3:10">
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="3:10">
+      <c r="C6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="3:10">
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10">
+      <c r="C7" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="3:10">
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="E7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1">
+        <v>100</v>
+      </c>
+      <c r="I7" s="1">
         <v>10</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="3:10">
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="3:10">
-      <c r="C6" s="4">
-        <v>1001</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="3:10">
-      <c r="C7" s="6">
-        <v>1002</v>
-      </c>
-      <c r="D7" s="6">
-        <v>2</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="7">
-        <v>100</v>
-      </c>
-      <c r="I7" s="7">
-        <v>10</v>
-      </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="3:10">
-      <c r="C8" s="6">
-        <v>1003</v>
-      </c>
-      <c r="D8" s="6">
-        <v>2</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="7">
-        <v>200</v>
-      </c>
-      <c r="I8" s="7">
-        <v>20</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" spans="3:10">
-      <c r="C9" s="6">
-        <v>1004</v>
-      </c>
-      <c r="D9" s="6">
-        <v>2</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="7">
-        <v>300</v>
-      </c>
-      <c r="I9" s="7">
-        <v>30</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="J9" s="5"/>
     </row>
     <row r="10" spans="3:10">
-      <c r="C10" s="6">
-        <v>1005</v>
-      </c>
-      <c r="D10" s="6">
-        <v>2</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="7">
-        <v>400</v>
-      </c>
-      <c r="I10" s="7">
-        <v>40</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" spans="3:10">
-      <c r="C11" s="6">
-        <v>1006</v>
-      </c>
-      <c r="D11" s="6">
-        <v>2</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="7">
-        <v>500</v>
-      </c>
-      <c r="I11" s="7">
-        <v>50</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="J11" s="5"/>
     </row>
     <row r="12" spans="3:10">
-      <c r="C12" s="6">
-        <v>1007</v>
-      </c>
-      <c r="D12" s="6">
-        <v>2</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="7">
-        <v>600</v>
-      </c>
-      <c r="I12" s="7">
-        <v>60</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="J12" s="5"/>
     </row>
     <row r="13" spans="3:10">
-      <c r="C13" s="6">
-        <v>1008</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="7">
-        <v>700</v>
-      </c>
-      <c r="I13" s="7">
-        <v>70</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="J13" s="5"/>
     </row>
     <row r="14" spans="3:10">
-      <c r="C14" s="6">
-        <v>1009</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="7">
-        <v>800</v>
-      </c>
-      <c r="I14" s="7">
-        <v>80</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="J14" s="5"/>
     </row>
     <row r="15" spans="3:10">
-      <c r="C15" s="6">
-        <v>1010</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="7">
-        <v>900</v>
-      </c>
-      <c r="I15" s="7">
-        <v>90</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="3:10">
-      <c r="C16" s="6">
-        <v>1011</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="7">
-        <v>1000</v>
-      </c>
-      <c r="I16" s="7">
-        <v>100</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="J16" s="5"/>
     </row>
     <row r="17" spans="3:10">
-      <c r="C17" s="6">
-        <v>1012</v>
-      </c>
-      <c r="D17" s="6">
-        <v>2</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="7">
-        <v>1100</v>
-      </c>
-      <c r="I17" s="7">
-        <v>110</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="J17" s="5"/>
     </row>
     <row r="18" spans="3:10">
-      <c r="C18" s="6">
-        <v>1013</v>
-      </c>
-      <c r="D18" s="6">
-        <v>2</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="7">
-        <v>1200</v>
-      </c>
-      <c r="I18" s="7">
-        <v>120</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="J18" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
